--- a/trpg-web/autochat.xlsx
+++ b/trpg-web/autochat.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="136">
   <si>
     <t>닉네임</t>
   </si>
@@ -23,34 +23,367 @@
     <t>댓글 내용</t>
   </si>
   <si>
-    <t>ㄱㄱ</t>
+    <t>배경</t>
+  </si>
+  <si>
+    <t>ㄹㅈㄷ</t>
+  </si>
+  <si>
+    <t>츠네</t>
+  </si>
+  <si>
+    <t>잘생겼다.</t>
+  </si>
+  <si>
+    <t>형님</t>
+  </si>
+  <si>
+    <t>에반데</t>
+  </si>
+  <si>
+    <t>참치</t>
+  </si>
+  <si>
+    <t>wwwwwww</t>
+  </si>
+  <si>
+    <t>화동동구리</t>
+  </si>
+  <si>
+    <t>내 통장은 통장이 아니라 통로야. 네 지갑으로 가는 고속도로.</t>
+  </si>
+  <si>
+    <t>CHU</t>
+  </si>
+  <si>
+    <t>얘들아, 노래 실력은 지하인데 미모는 지상계 실수가 분명하다.</t>
+  </si>
+  <si>
+    <t>랄셀</t>
+  </si>
+  <si>
+    <t>제 인생은 망했지만 우리 애가 행복하다면... 그걸로 됐습니다... (눈물)</t>
+  </si>
+  <si>
+    <t>살려줘!!</t>
+  </si>
+  <si>
+    <t>방금 찍은 체키 실물보다 예쁜데, 나 사실 카메라 렌즈였나 봐.</t>
+  </si>
+  <si>
+    <t>까까먹는토깽이</t>
+  </si>
+  <si>
+    <t>라이브 듣고 귀가 나았어요. 너무 충격받아서 귀가 스스로 닫혔거든요.</t>
+  </si>
+  <si>
+    <t>대학교6학년</t>
+  </si>
+  <si>
+    <t>노잼!</t>
+  </si>
+  <si>
+    <t>눈누난나</t>
+  </si>
+  <si>
+    <t>애들아 노래 조금만 더 크게 해줘... 내 심장박동 소리에 노래가 묻혀...</t>
+  </si>
+  <si>
+    <t>오타쿠감별사</t>
+  </si>
+  <si>
+    <t>의상이 너무 짧은 거 아니냐? 할미가 이불 들고 달려가고 싶다.</t>
+  </si>
+  <si>
+    <t>현타온다</t>
+  </si>
+  <si>
+    <t>실력도 없으면서 돈만 밝히는 거 눈에 다 보임.</t>
+  </si>
+  <si>
+    <t>무명판독기</t>
+  </si>
+  <si>
+    <t>저 정도 노래 실력이면 그냥 노래방 가서 부르는 게 나을 듯.</t>
+  </si>
+  <si>
+    <t>아이돌전문가</t>
+  </si>
+  <si>
+    <t>안무 대충 추는 거 보니까 이제 뜰 생각도 없나 보네.</t>
+  </si>
+  <si>
+    <t>탈덕예정</t>
+  </si>
+  <si>
+    <t>가창력이 조금 아쉽지만, 얼굴이 4K 화질이라서 귀가 양보하기로 함.</t>
+  </si>
+  <si>
+    <t>독설가K</t>
+  </si>
+  <si>
+    <t>지하돌은 지하에 있는 이유가 다 있다. 비주얼 처참하네.</t>
+  </si>
+  <si>
+    <t>팩트폭격기</t>
+  </si>
+  <si>
+    <t>보정 없으면 사진이랑 실물 차이 너무 심함. 사기 수준.</t>
+  </si>
+  <si>
+    <t>익명82</t>
+  </si>
+  <si>
+    <t>얘네는 노래 연습 안 하고 SNS만 하나 봐?</t>
+  </si>
+  <si>
+    <t>굿즈수집가</t>
+  </si>
+  <si>
+    <t>저번 라이브 때 음이탈 난 거 아직도 생각나서 소름 돋음.</t>
+  </si>
+  <si>
+    <t>텅장맨</t>
+  </si>
+  <si>
+    <t>돈 쏟아붓는 오타쿠들만 불쌍하지, 쟤는 너네 이름도 기억 못 해.</t>
+  </si>
+  <si>
+    <t>안티아님</t>
+  </si>
+  <si>
+    <t>실력 비판하는 건데 왜 악플이라고 함? 진짜 못함.</t>
+  </si>
+  <si>
+    <t>일침꾼</t>
+  </si>
+  <si>
+    <t>유령회원</t>
+  </si>
+  <si>
+    <t>체키노예</t>
+  </si>
+  <si>
+    <t>체키 찍을 때만 웃고 뒤 돌면 정색하는 거 다 봤다.</t>
+  </si>
+  <si>
+    <t>라이브빌런</t>
+  </si>
+  <si>
+    <t>냉정남</t>
+  </si>
+  <si>
+    <t>지하돌이 아니라 지상 최대의 선물이다 진짜.</t>
+  </si>
+  <si>
+    <t>멘탈갑</t>
+  </si>
+  <si>
+    <t>SNS에 우울한 척 글 좀 그만 올려라, 관심 구걸 적당히.</t>
+  </si>
+  <si>
+    <t>비운의오타</t>
+  </si>
+  <si>
+    <t>코멘트러</t>
+  </si>
+  <si>
+    <t>무지성비판</t>
+  </si>
+  <si>
+    <t>그냥 은퇴하고 알바나 해라. 재능이 아예 없음.</t>
+  </si>
+  <si>
+    <t>지하의신</t>
+  </si>
+  <si>
+    <t>이 그룹은 메인 보컬 빼고 다 들러리네. 존재 이유가 뭐임?</t>
+  </si>
+  <si>
+    <t>안목높음</t>
+  </si>
+  <si>
+    <t>이 정도면 국가에서 문화재로 지정해야 하는 거 아님?</t>
+  </si>
+  <si>
+    <t>회의론자</t>
+  </si>
+  <si>
+    <t>지상으로 올라가지 마... 나만 알고 싶단 말이야... 아니 사실 성공해... 아니 하지 마...</t>
+  </si>
+  <si>
+    <t>단호박</t>
+  </si>
+  <si>
+    <t>춤선이 너무 둔함. 몸치 아니야?</t>
+  </si>
+  <si>
+    <t>팩트만말함</t>
+  </si>
+  <si>
+    <t>인성 논란 터질 때부터 알아봤다. 역시나네.</t>
+  </si>
+  <si>
+    <t>구경꾼</t>
+  </si>
+  <si>
+    <t>얼굴 믿고 설치는데 그 얼굴도 사실 평범함.</t>
+  </si>
+  <si>
+    <t>비판적시각</t>
+  </si>
+  <si>
+    <t>팬들이 오냐오냐해주니까 자기가 뭐라도 된 줄 아나 봄.</t>
+  </si>
+  <si>
+    <t>시니컬J</t>
+  </si>
+  <si>
+    <t>얘네 소속사는 애들 관리 안 하냐? 비주얼 관리가 전혀 안 됨.</t>
+  </si>
+  <si>
+    <t>프로불편러</t>
+  </si>
+  <si>
+    <t>멘트할 때마다 갑분싸 만드는데 제발 대본이라도 써와라.</t>
+  </si>
+  <si>
+    <t>어둠의팬</t>
+  </si>
+  <si>
+    <t>이번 신곡 역대급으로 구림. 돈 벌 생각이 있는 건가.</t>
+  </si>
+  <si>
+    <t>칼답러</t>
+  </si>
+  <si>
+    <t>SNS 답변 차별하는 거 보니까 정떨어진다.</t>
+  </si>
+  <si>
+    <t>가성비충</t>
+  </si>
+  <si>
+    <t>입장료 3만 원도 아까운 공연 퀄리티.</t>
+  </si>
+  <si>
+    <t>쓴소리맨</t>
+  </si>
+  <si>
+    <t>너 말고 다른 애가 센터였으면 진작 떴을 텐데.</t>
+  </si>
+  <si>
+    <t>분석가</t>
+  </si>
+  <si>
+    <t>그룹 내에서 왕따 시키는 거 티 남. 분위기 살벌하네.</t>
+  </si>
+  <si>
+    <t>비수</t>
+  </si>
+  <si>
+    <t>연예인병 걸려서 인사도 제대로 안 하네.</t>
+  </si>
+  <si>
+    <t>냉혹한평가</t>
+  </si>
+  <si>
+    <t>지하 아이돌 중에서도 최하위 수준임.</t>
+  </si>
+  <si>
+    <t>사이다댓글</t>
+  </si>
+  <si>
+    <t>실력 없으면 노력이라도 하던가, 둘 다 안 하네.</t>
+  </si>
+  <si>
+    <t>막말러</t>
+  </si>
+  <si>
+    <t>나 방금 카드 긁었는데 카드사에서 '님 제발 그만'이라고 문자 옴.</t>
+  </si>
+  <si>
+    <t>현실직시</t>
+  </si>
+  <si>
+    <t>얘네는 5년 뒤에도 똑같이 지하 공연장에 있을 듯.</t>
+  </si>
+  <si>
+    <t>그림자</t>
+  </si>
+  <si>
+    <t>인지도도 없으면서 콧대만 높아서 짜증 남.</t>
+  </si>
+  <si>
+    <t>냉소주의</t>
+  </si>
+  <si>
+    <t>얘 때문에 그룹 전체 이미지만 나빠지는 중.</t>
+  </si>
+  <si>
+    <t>트러블메이커</t>
+  </si>
+  <si>
+    <t>wwwwwwwwwwwwwwwwwwwwwww</t>
+  </si>
+  <si>
+    <t>팩트체크</t>
+  </si>
+  <si>
+    <t>돌직구</t>
+  </si>
+  <si>
+    <t>무표정</t>
+  </si>
+  <si>
+    <t>비추천</t>
+  </si>
+  <si>
+    <t>돈 낭비하고 싶은 사람만 가세요. 절대 추천 안 함.</t>
+  </si>
+  <si>
+    <t>핀셋비판</t>
+  </si>
+  <si>
+    <t>안무 틀려놓고 웃으면서 넘기는 거 진짜 꼴 보기 싫다.</t>
+  </si>
+  <si>
+    <t>노필터</t>
+  </si>
+  <si>
+    <t>이제 나이도 있는데 슬슬 그만두고 취업 준비나 하지.</t>
+  </si>
+  <si>
+    <t>회의감</t>
+  </si>
+  <si>
+    <t>응원봉 흔드는 시간이 아깝게 느껴지는 공연이었음.</t>
+  </si>
+  <si>
+    <t>마지막경고</t>
+  </si>
+  <si>
+    <t>이번에도 성적 안 나오면 그냥 해체해라. 민폐다.</t>
+  </si>
+  <si>
+    <t>ㄹㄹ</t>
+  </si>
+  <si>
+    <t>ㄹㄹㄹㄹ</t>
+  </si>
+  <si>
+    <t>ㄹㄹㄹㄹㄹㄹ</t>
+  </si>
+  <si>
+    <t>ㄹㄹㄹ</t>
+  </si>
+  <si>
+    <t>ㄹㄹㄹㄹㄹㄹㄹㄹ</t>
+  </si>
+  <si>
+    <t>ㄹㄹㄹㄹㄹ</t>
   </si>
   <si>
     <t>ㄴㄴ</t>
-  </si>
-  <si>
-    <t>ㄷㄷ</t>
-  </si>
-  <si>
-    <t>ㄹㄹ</t>
-  </si>
-  <si>
-    <t>ㅁㅁ</t>
-  </si>
-  <si>
-    <t>ㄹㄹㄹㄹ</t>
-  </si>
-  <si>
-    <t>ㄹㄹㄹㄹㄹㄹ</t>
-  </si>
-  <si>
-    <t>ㄹㄹㄹ</t>
-  </si>
-  <si>
-    <t>ㄹㄹㄹㄹㄹㄹㄹㄹ</t>
-  </si>
-  <si>
-    <t>ㄹㄹㄹㄹㄹ</t>
   </si>
   <si>
     <t>ㄴㄴㄴ</t>
@@ -96,7 +429,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -114,6 +447,10 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -129,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -138,6 +475,12 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -381,43 +724,491 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
-        <v>1.0</v>
+      <c r="A2" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
-        <v>2.0</v>
+      <c r="A3" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
-        <v>3.0</v>
+      <c r="A4" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2">
-        <v>4.0</v>
+      <c r="A5" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2">
-        <v>5.0</v>
+      <c r="A6" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -442,7 +1233,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>116</v>
       </c>
       <c r="B2" s="2">
         <v>56.0</v>
@@ -450,7 +1241,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>117</v>
       </c>
       <c r="B3" s="2">
         <v>57.0</v>
@@ -458,7 +1249,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="B4" s="2">
         <v>36.0</v>
@@ -466,7 +1257,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="B5" s="2">
         <v>26.0</v>
@@ -474,7 +1265,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="B6" s="2">
         <v>16.0</v>
@@ -482,7 +1273,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="B7" s="2">
         <v>76.0</v>
@@ -513,7 +1304,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>122</v>
       </c>
       <c r="B2" s="2">
         <v>56.0</v>
@@ -521,7 +1312,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="B3" s="2">
         <v>57.0</v>
@@ -529,7 +1320,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>124</v>
       </c>
       <c r="B4" s="2">
         <v>36.0</v>
@@ -537,7 +1328,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>125</v>
       </c>
       <c r="B5" s="2">
         <v>26.0</v>
@@ -545,7 +1336,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>125</v>
       </c>
       <c r="B6" s="2">
         <v>16.0</v>
@@ -553,7 +1344,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="B7" s="2">
         <v>76.0</v>
@@ -581,7 +1372,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>126</v>
       </c>
       <c r="B2" s="2">
         <v>56.0</v>
@@ -589,7 +1380,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>127</v>
       </c>
       <c r="B3" s="2">
         <v>57.0</v>
@@ -597,7 +1388,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>128</v>
       </c>
       <c r="B4" s="2">
         <v>36.0</v>
@@ -605,7 +1396,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="B5" s="2">
         <v>26.0</v>
@@ -613,7 +1404,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>130</v>
       </c>
       <c r="B6" s="2">
         <v>16.0</v>
@@ -646,7 +1437,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="B2" s="2">
         <v>56.0</v>
@@ -654,7 +1445,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="B3" s="2">
         <v>57.0</v>
@@ -662,7 +1453,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="B4" s="2">
         <v>36.0</v>
@@ -670,7 +1461,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>23</v>
+        <v>134</v>
       </c>
       <c r="B5" s="2">
         <v>26.0</v>
@@ -678,7 +1469,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="B6" s="2">
         <v>16.0</v>

--- a/trpg-web/autochat.xlsx
+++ b/trpg-web/autochat.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="148">
   <si>
     <t>닉네임</t>
   </si>
@@ -50,337 +50,373 @@
     <t>화동동구리</t>
   </si>
   <si>
+    <t>이거 뭐임?</t>
+  </si>
+  <si>
+    <t>CHU</t>
+  </si>
+  <si>
+    <t>뭐임?</t>
+  </si>
+  <si>
+    <t>랄셀</t>
+  </si>
+  <si>
+    <t>살려줘!!</t>
+  </si>
+  <si>
+    <t>까까먹는토깽이</t>
+  </si>
+  <si>
+    <t>대학교6학년</t>
+  </si>
+  <si>
+    <t>눈누난나</t>
+  </si>
+  <si>
+    <t>오타쿠감별사</t>
+  </si>
+  <si>
+    <t>현타온다</t>
+  </si>
+  <si>
+    <t>무명판독기</t>
+  </si>
+  <si>
+    <t>아이돌전문가</t>
+  </si>
+  <si>
+    <t>엥?</t>
+  </si>
+  <si>
+    <t>탈덕예정</t>
+  </si>
+  <si>
+    <t>뭐야?</t>
+  </si>
+  <si>
+    <t>독설가K</t>
+  </si>
+  <si>
+    <t>팩트폭격기</t>
+  </si>
+  <si>
+    <t>익명82</t>
+  </si>
+  <si>
+    <t>응?</t>
+  </si>
+  <si>
+    <t>굿즈수집가</t>
+  </si>
+  <si>
+    <t>설명좀</t>
+  </si>
+  <si>
+    <t>텅장맨</t>
+  </si>
+  <si>
+    <t>안티아님</t>
+  </si>
+  <si>
+    <t>일침꾼</t>
+  </si>
+  <si>
+    <t>유령회원</t>
+  </si>
+  <si>
+    <t>체키노예</t>
+  </si>
+  <si>
+    <t>설명좀요</t>
+  </si>
+  <si>
+    <t>라이브빌런</t>
+  </si>
+  <si>
+    <t>냉정남</t>
+  </si>
+  <si>
+    <t>멘탈갑</t>
+  </si>
+  <si>
+    <t>비운의오타</t>
+  </si>
+  <si>
+    <t>엥</t>
+  </si>
+  <si>
+    <t>코멘트러</t>
+  </si>
+  <si>
+    <t>뭐냐이거</t>
+  </si>
+  <si>
+    <t>무지성비판</t>
+  </si>
+  <si>
+    <t>지하의신</t>
+  </si>
+  <si>
+    <t>안목높음</t>
+  </si>
+  <si>
+    <t>회의론자</t>
+  </si>
+  <si>
+    <t>단호박</t>
+  </si>
+  <si>
+    <t>팩트만말함</t>
+  </si>
+  <si>
+    <t>구경꾼</t>
+  </si>
+  <si>
+    <t>비판적시각</t>
+  </si>
+  <si>
+    <t>시니컬J</t>
+  </si>
+  <si>
+    <t>프로불편러</t>
+  </si>
+  <si>
+    <t>어둠의팬</t>
+  </si>
+  <si>
+    <t>와 망돌이 있네</t>
+  </si>
+  <si>
+    <t>칼답러</t>
+  </si>
+  <si>
+    <t>가성비충</t>
+  </si>
+  <si>
+    <t>쓴소리맨</t>
+  </si>
+  <si>
+    <t>분석가</t>
+  </si>
+  <si>
+    <t>비수</t>
+  </si>
+  <si>
+    <t>냉혹한평가</t>
+  </si>
+  <si>
+    <t>사이다댓글</t>
+  </si>
+  <si>
+    <t>막말러</t>
+  </si>
+  <si>
+    <t>현실직시</t>
+  </si>
+  <si>
+    <t>그림자</t>
+  </si>
+  <si>
+    <t>아니그러니까이게뭐냐고이것들아</t>
+  </si>
+  <si>
+    <t>냉소주의</t>
+  </si>
+  <si>
+    <t>나도모른다고</t>
+  </si>
+  <si>
+    <t>트러블메이커</t>
+  </si>
+  <si>
+    <t>와 저거 뭐임 귀여워</t>
+  </si>
+  <si>
+    <t>팩트체크</t>
+  </si>
+  <si>
+    <t>센터 귀엽다</t>
+  </si>
+  <si>
+    <t>돌직구</t>
+  </si>
+  <si>
+    <t>와 저 금발 뭐임 개섹시</t>
+  </si>
+  <si>
+    <t>무표정</t>
+  </si>
+  <si>
+    <t>와 분홍머리 뭐야 귀여워~~~</t>
+  </si>
+  <si>
+    <t>비추천</t>
+  </si>
+  <si>
+    <t>저 퇴폐미 있는남자누구임나지금급함ㅎ헉헉</t>
+  </si>
+  <si>
+    <t>핀셋비판</t>
+  </si>
+  <si>
+    <t>노필터</t>
+  </si>
+  <si>
+    <t>회의감</t>
+  </si>
+  <si>
+    <t>마지막경고</t>
+  </si>
+  <si>
+    <t>리더 개같이 생김.(욕아님)</t>
+  </si>
+  <si>
     <t>내 통장은 통장이 아니라 통로야. 네 지갑으로 가는 고속도로.</t>
   </si>
   <si>
-    <t>CHU</t>
-  </si>
-  <si>
     <t>얘들아, 노래 실력은 지하인데 미모는 지상계 실수가 분명하다.</t>
   </si>
   <si>
-    <t>랄셀</t>
-  </si>
-  <si>
     <t>제 인생은 망했지만 우리 애가 행복하다면... 그걸로 됐습니다... (눈물)</t>
   </si>
   <si>
-    <t>살려줘!!</t>
-  </si>
-  <si>
     <t>방금 찍은 체키 실물보다 예쁜데, 나 사실 카메라 렌즈였나 봐.</t>
   </si>
   <si>
-    <t>까까먹는토깽이</t>
-  </si>
-  <si>
     <t>라이브 듣고 귀가 나았어요. 너무 충격받아서 귀가 스스로 닫혔거든요.</t>
   </si>
   <si>
-    <t>대학교6학년</t>
-  </si>
-  <si>
     <t>노잼!</t>
   </si>
   <si>
-    <t>눈누난나</t>
-  </si>
-  <si>
     <t>애들아 노래 조금만 더 크게 해줘... 내 심장박동 소리에 노래가 묻혀...</t>
   </si>
   <si>
-    <t>오타쿠감별사</t>
-  </si>
-  <si>
     <t>의상이 너무 짧은 거 아니냐? 할미가 이불 들고 달려가고 싶다.</t>
   </si>
   <si>
-    <t>현타온다</t>
-  </si>
-  <si>
     <t>실력도 없으면서 돈만 밝히는 거 눈에 다 보임.</t>
   </si>
   <si>
-    <t>무명판독기</t>
-  </si>
-  <si>
     <t>저 정도 노래 실력이면 그냥 노래방 가서 부르는 게 나을 듯.</t>
   </si>
   <si>
-    <t>아이돌전문가</t>
-  </si>
-  <si>
     <t>안무 대충 추는 거 보니까 이제 뜰 생각도 없나 보네.</t>
   </si>
   <si>
-    <t>탈덕예정</t>
-  </si>
-  <si>
     <t>가창력이 조금 아쉽지만, 얼굴이 4K 화질이라서 귀가 양보하기로 함.</t>
   </si>
   <si>
-    <t>독설가K</t>
-  </si>
-  <si>
     <t>지하돌은 지하에 있는 이유가 다 있다. 비주얼 처참하네.</t>
   </si>
   <si>
-    <t>팩트폭격기</t>
-  </si>
-  <si>
     <t>보정 없으면 사진이랑 실물 차이 너무 심함. 사기 수준.</t>
   </si>
   <si>
-    <t>익명82</t>
-  </si>
-  <si>
     <t>얘네는 노래 연습 안 하고 SNS만 하나 봐?</t>
   </si>
   <si>
-    <t>굿즈수집가</t>
-  </si>
-  <si>
     <t>저번 라이브 때 음이탈 난 거 아직도 생각나서 소름 돋음.</t>
   </si>
   <si>
-    <t>텅장맨</t>
-  </si>
-  <si>
     <t>돈 쏟아붓는 오타쿠들만 불쌍하지, 쟤는 너네 이름도 기억 못 해.</t>
   </si>
   <si>
-    <t>안티아님</t>
-  </si>
-  <si>
     <t>실력 비판하는 건데 왜 악플이라고 함? 진짜 못함.</t>
   </si>
   <si>
-    <t>일침꾼</t>
-  </si>
-  <si>
-    <t>유령회원</t>
-  </si>
-  <si>
-    <t>체키노예</t>
-  </si>
-  <si>
     <t>체키 찍을 때만 웃고 뒤 돌면 정색하는 거 다 봤다.</t>
   </si>
   <si>
-    <t>라이브빌런</t>
-  </si>
-  <si>
-    <t>냉정남</t>
-  </si>
-  <si>
     <t>지하돌이 아니라 지상 최대의 선물이다 진짜.</t>
   </si>
   <si>
-    <t>멘탈갑</t>
-  </si>
-  <si>
     <t>SNS에 우울한 척 글 좀 그만 올려라, 관심 구걸 적당히.</t>
   </si>
   <si>
-    <t>비운의오타</t>
-  </si>
-  <si>
-    <t>코멘트러</t>
-  </si>
-  <si>
-    <t>무지성비판</t>
-  </si>
-  <si>
     <t>그냥 은퇴하고 알바나 해라. 재능이 아예 없음.</t>
   </si>
   <si>
-    <t>지하의신</t>
-  </si>
-  <si>
     <t>이 그룹은 메인 보컬 빼고 다 들러리네. 존재 이유가 뭐임?</t>
   </si>
   <si>
-    <t>안목높음</t>
-  </si>
-  <si>
     <t>이 정도면 국가에서 문화재로 지정해야 하는 거 아님?</t>
   </si>
   <si>
-    <t>회의론자</t>
-  </si>
-  <si>
     <t>지상으로 올라가지 마... 나만 알고 싶단 말이야... 아니 사실 성공해... 아니 하지 마...</t>
   </si>
   <si>
-    <t>단호박</t>
-  </si>
-  <si>
     <t>춤선이 너무 둔함. 몸치 아니야?</t>
   </si>
   <si>
-    <t>팩트만말함</t>
-  </si>
-  <si>
     <t>인성 논란 터질 때부터 알아봤다. 역시나네.</t>
   </si>
   <si>
-    <t>구경꾼</t>
-  </si>
-  <si>
     <t>얼굴 믿고 설치는데 그 얼굴도 사실 평범함.</t>
   </si>
   <si>
-    <t>비판적시각</t>
-  </si>
-  <si>
     <t>팬들이 오냐오냐해주니까 자기가 뭐라도 된 줄 아나 봄.</t>
   </si>
   <si>
-    <t>시니컬J</t>
-  </si>
-  <si>
     <t>얘네 소속사는 애들 관리 안 하냐? 비주얼 관리가 전혀 안 됨.</t>
   </si>
   <si>
-    <t>프로불편러</t>
-  </si>
-  <si>
     <t>멘트할 때마다 갑분싸 만드는데 제발 대본이라도 써와라.</t>
   </si>
   <si>
-    <t>어둠의팬</t>
-  </si>
-  <si>
     <t>이번 신곡 역대급으로 구림. 돈 벌 생각이 있는 건가.</t>
   </si>
   <si>
-    <t>칼답러</t>
-  </si>
-  <si>
     <t>SNS 답변 차별하는 거 보니까 정떨어진다.</t>
   </si>
   <si>
-    <t>가성비충</t>
-  </si>
-  <si>
     <t>입장료 3만 원도 아까운 공연 퀄리티.</t>
   </si>
   <si>
-    <t>쓴소리맨</t>
-  </si>
-  <si>
     <t>너 말고 다른 애가 센터였으면 진작 떴을 텐데.</t>
   </si>
   <si>
-    <t>분석가</t>
-  </si>
-  <si>
     <t>그룹 내에서 왕따 시키는 거 티 남. 분위기 살벌하네.</t>
   </si>
   <si>
-    <t>비수</t>
-  </si>
-  <si>
     <t>연예인병 걸려서 인사도 제대로 안 하네.</t>
   </si>
   <si>
-    <t>냉혹한평가</t>
-  </si>
-  <si>
     <t>지하 아이돌 중에서도 최하위 수준임.</t>
   </si>
   <si>
-    <t>사이다댓글</t>
-  </si>
-  <si>
     <t>실력 없으면 노력이라도 하던가, 둘 다 안 하네.</t>
   </si>
   <si>
-    <t>막말러</t>
-  </si>
-  <si>
     <t>나 방금 카드 긁었는데 카드사에서 '님 제발 그만'이라고 문자 옴.</t>
   </si>
   <si>
-    <t>현실직시</t>
-  </si>
-  <si>
     <t>얘네는 5년 뒤에도 똑같이 지하 공연장에 있을 듯.</t>
   </si>
   <si>
-    <t>그림자</t>
-  </si>
-  <si>
     <t>인지도도 없으면서 콧대만 높아서 짜증 남.</t>
   </si>
   <si>
-    <t>냉소주의</t>
-  </si>
-  <si>
     <t>얘 때문에 그룹 전체 이미지만 나빠지는 중.</t>
   </si>
   <si>
-    <t>트러블메이커</t>
-  </si>
-  <si>
     <t>wwwwwwwwwwwwwwwwwwwwwww</t>
   </si>
   <si>
-    <t>팩트체크</t>
-  </si>
-  <si>
-    <t>돌직구</t>
-  </si>
-  <si>
-    <t>무표정</t>
-  </si>
-  <si>
-    <t>비추천</t>
-  </si>
-  <si>
     <t>돈 낭비하고 싶은 사람만 가세요. 절대 추천 안 함.</t>
   </si>
   <si>
-    <t>핀셋비판</t>
-  </si>
-  <si>
     <t>안무 틀려놓고 웃으면서 넘기는 거 진짜 꼴 보기 싫다.</t>
   </si>
   <si>
-    <t>노필터</t>
-  </si>
-  <si>
     <t>이제 나이도 있는데 슬슬 그만두고 취업 준비나 하지.</t>
   </si>
   <si>
-    <t>회의감</t>
-  </si>
-  <si>
     <t>응원봉 흔드는 시간이 아깝게 느껴지는 공연이었음.</t>
   </si>
   <si>
-    <t>마지막경고</t>
-  </si>
-  <si>
     <t>이번에도 성적 안 나오면 그냥 해체해라. 민폐다.</t>
-  </si>
-  <si>
-    <t>ㄹㄹ</t>
-  </si>
-  <si>
-    <t>ㄹㄹㄹㄹ</t>
-  </si>
-  <si>
-    <t>ㄹㄹㄹㄹㄹㄹ</t>
-  </si>
-  <si>
-    <t>ㄹㄹㄹ</t>
-  </si>
-  <si>
-    <t>ㄹㄹㄹㄹㄹㄹㄹㄹ</t>
-  </si>
-  <si>
-    <t>ㄹㄹㄹㄹㄹ</t>
   </si>
   <si>
     <t>ㄴㄴ</t>
@@ -776,439 +812,439 @@
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>31</v>
+        <v>22</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>35</v>
+        <v>26</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>39</v>
+        <v>28</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>41</v>
+        <v>30</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>45</v>
+        <v>33</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>49</v>
+        <v>36</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>52</v>
+        <v>39</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>54</v>
+        <v>40</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>58</v>
+        <v>45</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>60</v>
+        <v>46</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>70</v>
+        <v>51</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>72</v>
+        <v>52</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>74</v>
+        <v>53</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>76</v>
+        <v>54</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>78</v>
+        <v>55</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>80</v>
+        <v>57</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>82</v>
+        <v>58</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>84</v>
+        <v>59</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>86</v>
+        <v>60</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>88</v>
+        <v>61</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>90</v>
+        <v>62</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>96</v>
+        <v>65</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>98</v>
+        <v>66</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>100</v>
+        <v>68</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>107</v>
+        <v>78</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>109</v>
+        <v>80</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>111</v>
+        <v>81</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>113</v>
+        <v>82</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>115</v>
+        <v>83</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1233,54 +1269,459 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B2" s="2">
-        <v>56.0</v>
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" s="2">
-        <v>57.0</v>
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B4" s="2">
-        <v>36.0</v>
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B5" s="2">
-        <v>26.0</v>
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B6" s="2">
-        <v>16.0</v>
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B7" s="2">
-        <v>76.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>133</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -1304,7 +1745,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="B2" s="2">
         <v>56.0</v>
@@ -1312,7 +1753,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B3" s="2">
         <v>57.0</v>
@@ -1320,7 +1761,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B4" s="2">
         <v>36.0</v>
@@ -1328,7 +1769,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="B5" s="2">
         <v>26.0</v>
@@ -1336,7 +1777,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="B6" s="2">
         <v>16.0</v>
@@ -1344,7 +1785,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B7" s="2">
         <v>76.0</v>
@@ -1372,7 +1813,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B2" s="2">
         <v>56.0</v>
@@ -1380,7 +1821,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="B3" s="2">
         <v>57.0</v>
@@ -1388,7 +1829,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B4" s="2">
         <v>36.0</v>
@@ -1396,7 +1837,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B5" s="2">
         <v>26.0</v>
@@ -1404,7 +1845,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="B6" s="2">
         <v>16.0</v>
@@ -1437,7 +1878,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B2" s="2">
         <v>56.0</v>
@@ -1445,7 +1886,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="B3" s="2">
         <v>57.0</v>
@@ -1453,7 +1894,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="B4" s="2">
         <v>36.0</v>
@@ -1461,7 +1902,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="B5" s="2">
         <v>26.0</v>
@@ -1469,7 +1910,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B6" s="2">
         <v>16.0</v>
